--- a/exports/JUBLFOOD_full_report.xlsx
+++ b/exports/JUBLFOOD_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q68"/>
+  <dimension ref="A1:U68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>5.93</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44580.55208333334</v>
+        <v>44581.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>749</v>
+        <v>735.45</v>
       </c>
       <c r="I2" t="n">
         <v>743.9812768338089</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.18</v>
+        <v>-2.97</v>
       </c>
       <c r="L2" t="n">
-        <v>2.07</v>
+        <v>3.07</v>
       </c>
       <c r="M2" t="n">
         <v>0.4</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>7.23</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44630.55208333334</v>
+        <v>44631.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>552</v>
+        <v>563.45</v>
       </c>
       <c r="I3" t="n">
         <v>555.1829616566999</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K3" t="n">
-        <v>24.94</v>
+        <v>23.39</v>
       </c>
       <c r="L3" t="n">
         <v>2.36</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>10.59</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44631.55208333334</v>
+        <v>44634.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>573</v>
+        <v>498.8</v>
       </c>
       <c r="I4" t="n">
         <v>515.194445155893</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>1.69</v>
+        <v>-11.47</v>
       </c>
       <c r="L4" t="n">
-        <v>3.16</v>
+        <v>13.21</v>
       </c>
       <c r="M4" t="n">
-        <v>0.17</v>
+        <v>6.63</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>12.25</v>
       </c>
       <c r="O4" t="n">
         <v>3.8</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>17.32</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44652.55208333334</v>
+        <v>44655.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>545.4</v>
+        <v>552.6</v>
       </c>
       <c r="I5" t="n">
         <v>551.5881311351624</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.34</v>
+        <v>-10.79</v>
       </c>
       <c r="L5" t="n">
-        <v>9.6</v>
+        <v>11.51</v>
       </c>
       <c r="M5" t="n">
         <v>1.82</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>6.48</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44677.55208333334</v>
+        <v>44678.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>548</v>
+        <v>531</v>
       </c>
       <c r="I6" t="n">
         <v>534.6553281597469</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.83</v>
+        <v>-3.91</v>
       </c>
       <c r="L6" t="n">
         <v>4.18</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>12.17</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44707.55208333334</v>
+        <v>44708.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>489.9</v>
+        <v>510.7</v>
       </c>
       <c r="I7" t="n">
         <v>501.0770203755592</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K7" t="n">
-        <v>7.74</v>
+        <v>3.82</v>
       </c>
       <c r="L7" t="n">
         <v>5.84</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>10.47</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44720.38541666666</v>
+        <v>44720.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>520.55</v>
+        <v>515.4</v>
       </c>
       <c r="I8" t="n">
         <v>515.6414542369615</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>1.93</v>
+        <v>0.92</v>
       </c>
       <c r="L8" t="n">
         <v>4.12</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1040,25 @@
         <v>7.93</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>532</v>
+        <v>545.6</v>
       </c>
       <c r="I9" t="n">
         <v>533.4561508285205</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-3.22</v>
+        <v>-5.86</v>
       </c>
       <c r="L9" t="n">
-        <v>4.44</v>
+        <v>6.29</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="N9" t="n">
         <v>4.55</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.67</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44768.38541666666</v>
+        <v>44768.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>555.85</v>
+        <v>551</v>
       </c>
       <c r="I10" t="n">
         <v>552.6957456243824</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>1.88</v>
+        <v>0.99</v>
       </c>
       <c r="L10" t="n">
         <v>7.24</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>6.97</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44783.55208333334</v>
+        <v>44784.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>566.5</v>
+        <v>591.6</v>
       </c>
       <c r="I11" t="n">
         <v>585.8323471083226</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.81</v>
+        <v>-7.37</v>
       </c>
       <c r="L11" t="n">
         <v>8.359999999999999</v>
@@ -1068,7 +1199,7 @@
         <v>2.2</v>
       </c>
       <c r="N11" t="n">
-        <v>1.56</v>
+        <v>3.87</v>
       </c>
       <c r="O11" t="n">
         <v>-3.62</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>593.25</v>
+        <v>572.8</v>
       </c>
       <c r="I12" t="n">
         <v>581.7883980293248</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K12" t="n">
-        <v>0.28</v>
+        <v>-3.18</v>
       </c>
       <c r="L12" t="n">
         <v>3.47</v>
       </c>
       <c r="M12" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="N12" t="n">
-        <v>4.16</v>
+        <v>4.88</v>
       </c>
       <c r="O12" t="n">
         <v>3.87</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>9.74</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44802.55208333334</v>
+        <v>44803.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>603.5</v>
+        <v>616.2</v>
       </c>
       <c r="I13" t="n">
         <v>613.17387455296</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.36</v>
+        <v>-7.58</v>
       </c>
       <c r="L13" t="n">
-        <v>5.91</v>
+        <v>8.01</v>
       </c>
       <c r="M13" t="n">
         <v>1.36</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.61</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44845.38541666666</v>
+        <v>44845.55208333334</v>
       </c>
       <c r="H14" t="n">
-        <v>606</v>
+        <v>600.4</v>
       </c>
       <c r="I14" t="n">
         <v>600.7936646222373</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.66</v>
+        <v>-2.56</v>
       </c>
       <c r="L14" t="n">
         <v>5.63</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>6.85</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44944.55208333334</v>
+        <v>44945.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>504.05</v>
+        <v>509.2</v>
       </c>
       <c r="I15" t="n">
         <v>508.950387315409</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>99</v>
+        <v>99.83333333333333</v>
       </c>
       <c r="K15" t="n">
-        <v>16.05</v>
+        <v>15.19</v>
       </c>
       <c r="L15" t="n">
         <v>4.56</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>138</v>
+        <v>139</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>5.17</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>495.9</v>
+        <v>478.55</v>
       </c>
       <c r="I16" t="n">
         <v>491.6390164505121</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.61</v>
+        <v>-6.02</v>
       </c>
       <c r="L16" t="n">
-        <v>3.38</v>
+        <v>6.66</v>
       </c>
       <c r="M16" t="n">
         <v>0.41</v>
       </c>
       <c r="N16" t="n">
-        <v>1.12</v>
+        <v>2.25</v>
       </c>
       <c r="O16" t="n">
         <v>1.28</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>6.71</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44993.55208333334</v>
+        <v>44994.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>457</v>
+        <v>464.35</v>
       </c>
       <c r="I17" t="n">
         <v>458.3529407446451</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K17" t="n">
-        <v>4.5</v>
+        <v>2.97</v>
       </c>
       <c r="L17" t="n">
         <v>4.88</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>6.35</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>442.1</v>
+        <v>428.25</v>
       </c>
       <c r="I18" t="n">
         <v>437.6876901376103</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.79</v>
+        <v>-7.77</v>
       </c>
       <c r="L18" t="n">
-        <v>4.97</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="M18" t="n">
         <v>0.96</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>7.74</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45037.55208333334</v>
+        <v>45040.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>443.1</v>
+        <v>447.75</v>
       </c>
       <c r="I19" t="n">
         <v>443.3265217510741</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.47</v>
+        <v>-4.55</v>
       </c>
       <c r="L19" t="n">
         <v>5.29</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.14</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45100.38541666666</v>
+        <v>45100.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>488.35</v>
+        <v>480</v>
       </c>
       <c r="I20" t="n">
         <v>481.057112932359</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>60</v>
+        <v>60.16666666666666</v>
       </c>
       <c r="K20" t="n">
-        <v>9.07</v>
+        <v>7.2</v>
       </c>
       <c r="L20" t="n">
         <v>1.51</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>5.5</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45139.38541666666</v>
+        <v>45139.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>481.9</v>
+        <v>491</v>
       </c>
       <c r="I21" t="n">
         <v>486.1941582820273</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>38.83333333333334</v>
+        <v>39</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4</v>
+        <v>-2.29</v>
       </c>
       <c r="L21" t="n">
         <v>6.24</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.45</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45147.55208333334</v>
+        <v>45148.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>502.4</v>
+        <v>494.55</v>
       </c>
       <c r="I22" t="n">
         <v>496.4432010792811</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K22" t="n">
-        <v>2.32</v>
+        <v>0.72</v>
       </c>
       <c r="L22" t="n">
         <v>1.99</v>
@@ -1695,7 +1958,7 @@
         <v>0.24</v>
       </c>
       <c r="N22" t="n">
-        <v>1.34</v>
+        <v>2.07</v>
       </c>
       <c r="O22" t="n">
         <v>2.56</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>6.37</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45167.55208333334</v>
+        <v>45168.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>486</v>
+        <v>506.15</v>
       </c>
       <c r="I23" t="n">
         <v>500.854590640878</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K23" t="n">
-        <v>1.73</v>
+        <v>-2.35</v>
       </c>
       <c r="L23" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="M23" t="n">
         <v>0.76</v>
       </c>
       <c r="N23" t="n">
-        <v>1.55</v>
+        <v>4.27</v>
       </c>
       <c r="O23" t="n">
         <v>-2.07</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S23" t="b">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>6.52</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45182.55208333334</v>
+        <v>45183.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>519.5</v>
+        <v>517.9</v>
       </c>
       <c r="I24" t="n">
         <v>518.9369259468588</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K24" t="n">
-        <v>2.64</v>
+        <v>2.32</v>
       </c>
       <c r="L24" t="n">
         <v>4.02</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>6.29</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45195.55208333334</v>
+        <v>45196.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>545</v>
+        <v>554.4</v>
       </c>
       <c r="I25" t="n">
         <v>549.2536848878754</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.23</v>
+        <v>-7.05</v>
       </c>
       <c r="L25" t="n">
-        <v>5.85</v>
+        <v>7.32</v>
       </c>
       <c r="M25" t="n">
         <v>0.19</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.59</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>527.45</v>
+        <v>526.05</v>
       </c>
       <c r="I26" t="n">
         <v>527.3843598248519</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.86</v>
+        <v>-5.11</v>
       </c>
       <c r="L26" t="n">
         <v>5.74</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>4.12</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45245.55208333334</v>
+        <v>45246.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>515.7</v>
+        <v>527.15</v>
       </c>
       <c r="I27" t="n">
         <v>521.484406429675</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K27" t="n">
-        <v>1.97</v>
+        <v>-0.21</v>
       </c>
       <c r="L27" t="n">
         <v>2.42</v>
@@ -1980,7 +2303,7 @@
         <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="O27" t="n">
         <v>-0.65</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>4.9</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45296.55208333334</v>
+        <v>45299.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>556.3</v>
+        <v>538.45</v>
       </c>
       <c r="I28" t="n">
         <v>549.4194480802747</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>50.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K28" t="n">
-        <v>5.53</v>
+        <v>2.14</v>
       </c>
       <c r="L28" t="n">
         <v>2.3</v>
@@ -2037,7 +2372,7 @@
         <v>0.99</v>
       </c>
       <c r="N28" t="n">
-        <v>1.86</v>
+        <v>4.19</v>
       </c>
       <c r="O28" t="n">
         <v>2.35</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>6.42</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45338.38541666666</v>
+        <v>45338.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>492.75</v>
+        <v>496</v>
       </c>
       <c r="I29" t="n">
         <v>494.004207814069</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K29" t="n">
-        <v>8.49</v>
+        <v>7.88</v>
       </c>
       <c r="L29" t="n">
         <v>3.35</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>5.63</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45349.55208333334</v>
+        <v>45350.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>483.9</v>
+        <v>468.05</v>
       </c>
       <c r="I30" t="n">
         <v>479.9982622339908</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.44</v>
+        <v>-5.64</v>
       </c>
       <c r="L30" t="n">
-        <v>3.15</v>
+        <v>5.64</v>
       </c>
       <c r="M30" t="n">
         <v>0.2</v>
       </c>
       <c r="N30" t="n">
-        <v>2.39</v>
+        <v>2.92</v>
       </c>
       <c r="O30" t="n">
         <v>3.53</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>8.640000000000001</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45377.38541666666</v>
+        <v>45377.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="I31" t="n">
         <v>459.4594529566173</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K31" t="n">
-        <v>2.79</v>
+        <v>0.44</v>
       </c>
       <c r="L31" t="n">
         <v>4.05</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,25 +2627,25 @@
         <v>6.39</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45400.55208333334</v>
+        <v>45401.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>443.9</v>
+        <v>436.9</v>
       </c>
       <c r="I32" t="n">
         <v>443.4905848746486</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K32" t="n">
-        <v>-4.74</v>
+        <v>-6.24</v>
       </c>
       <c r="L32" t="n">
-        <v>5.52</v>
+        <v>7.81</v>
       </c>
       <c r="M32" t="n">
-        <v>0.85</v>
+        <v>1.22</v>
       </c>
       <c r="N32" t="n">
         <v>2.4</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>4.63</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45411.55208333334</v>
+        <v>45412.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>439.05</v>
+        <v>460.6</v>
       </c>
       <c r="I33" t="n">
         <v>452.7816287207463</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.49</v>
+        <v>-5.42</v>
       </c>
       <c r="L33" t="n">
-        <v>1.85</v>
+        <v>5.95</v>
       </c>
       <c r="M33" t="n">
         <v>1.11</v>
       </c>
       <c r="N33" t="n">
-        <v>0.92</v>
+        <v>5.23</v>
       </c>
       <c r="O33" t="n">
         <v>-1.78</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.54</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45565.55208333334</v>
+        <v>45566.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>681.75</v>
+        <v>657.4</v>
       </c>
       <c r="I34" t="n">
         <v>677.0280087020965</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>153.1666666666667</v>
+        <v>154</v>
       </c>
       <c r="K34" t="n">
-        <v>48.01</v>
+        <v>42.73</v>
       </c>
       <c r="L34" t="n">
         <v>4.69</v>
@@ -2379,7 +2786,7 @@
         <v>1.57</v>
       </c>
       <c r="N34" t="n">
-        <v>3.07</v>
+        <v>3.34</v>
       </c>
       <c r="O34" t="n">
         <v>5.23</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>211</v>
+        <v>212</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>6</v>
+      </c>
+      <c r="U34" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>7.91</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45602.38541666666</v>
+        <v>45602.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>598.05</v>
+        <v>602</v>
       </c>
       <c r="I35" t="n">
         <v>600.1332124402451</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>9.029999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="L35" t="n">
         <v>4.34</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>6.44</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45638.38541666666</v>
+        <v>45638.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>674.9</v>
+        <v>671.2</v>
       </c>
       <c r="I36" t="n">
         <v>673.4833412575568</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>35.83333333333334</v>
+        <v>36</v>
       </c>
       <c r="K36" t="n">
-        <v>12.11</v>
+        <v>11.5</v>
       </c>
       <c r="L36" t="n">
         <v>2.94</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>6.53</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45653.55208333334</v>
+        <v>45656.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>708.15</v>
+        <v>715.25</v>
       </c>
       <c r="I37" t="n">
         <v>711.2676654322674</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>15</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>-5.51</v>
+        <v>-6.56</v>
       </c>
       <c r="L37" t="n">
         <v>8</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>5.95</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45667.55208333334</v>
+        <v>45670.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>738.25</v>
+        <v>715</v>
       </c>
       <c r="I38" t="n">
         <v>732.1540887588826</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K38" t="n">
-        <v>3.22</v>
+        <v>-0.03</v>
       </c>
       <c r="L38" t="n">
         <v>1.42</v>
       </c>
       <c r="M38" t="n">
-        <v>0.3</v>
+        <v>1.38</v>
       </c>
       <c r="N38" t="n">
-        <v>1.29</v>
+        <v>4.23</v>
       </c>
       <c r="O38" t="n">
         <v>0.4</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>7.41</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>693</v>
+        <v>700.3</v>
       </c>
       <c r="I39" t="n">
         <v>693.0381885231864</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K39" t="n">
-        <v>3.08</v>
+        <v>2.06</v>
       </c>
       <c r="L39" t="n">
         <v>4.61</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>7.57</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45695.55208333334</v>
+        <v>45698.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>689.3</v>
+        <v>674.15</v>
       </c>
       <c r="I40" t="n">
         <v>676.4046119799194</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.57</v>
+        <v>-3.73</v>
       </c>
       <c r="L40" t="n">
-        <v>2.71</v>
+        <v>3.89</v>
       </c>
       <c r="M40" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="N40" t="n">
         <v>4.13</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>10.96</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45707.38541666666</v>
+        <v>45707.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>701.45</v>
+        <v>710</v>
       </c>
       <c r="I41" t="n">
         <v>707.5230783230425</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K41" t="n">
-        <v>-4.05</v>
+        <v>-5.32</v>
       </c>
       <c r="L41" t="n">
-        <v>4.5</v>
+        <v>5.56</v>
       </c>
       <c r="M41" t="n">
         <v>1.11</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>9.19</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45715.55208333334</v>
+        <v>45716.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>670</v>
+        <v>630.55</v>
       </c>
       <c r="I42" t="n">
         <v>658.8900091740503</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K42" t="n">
-        <v>-5.63</v>
+        <v>-11.19</v>
       </c>
       <c r="L42" t="n">
-        <v>6.18</v>
+        <v>12.23</v>
       </c>
       <c r="M42" t="n">
-        <v>0.44</v>
+        <v>1.79</v>
       </c>
       <c r="N42" t="n">
-        <v>3.17</v>
+        <v>6.95</v>
       </c>
       <c r="O42" t="n">
         <v>2.76</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>11.68</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>628</v>
+        <v>646.5</v>
       </c>
       <c r="I43" t="n">
         <v>638.7765098317738</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K43" t="n">
-        <v>0.4</v>
+        <v>-2.53</v>
       </c>
       <c r="L43" t="n">
         <v>4.55</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.789999999999999</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45785.38541666666</v>
+        <v>45785.55208333334</v>
       </c>
       <c r="H44" t="n">
-        <v>693.2</v>
+        <v>666.75</v>
       </c>
       <c r="I44" t="n">
         <v>674.3522629236948</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>50</v>
+        <v>50.16666666666666</v>
       </c>
       <c r="K44" t="n">
-        <v>7.22</v>
+        <v>3.13</v>
       </c>
       <c r="L44" t="n">
         <v>4.1</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>9.16</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45812.55208333334</v>
+        <v>45813.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>685</v>
+        <v>687.8</v>
       </c>
       <c r="I45" t="n">
         <v>685.2841967024946</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.74</v>
+        <v>-3.16</v>
       </c>
       <c r="L45" t="n">
         <v>6.84</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>4.96</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45820.38541666666</v>
+        <v>45820.55208333334</v>
       </c>
       <c r="H46" t="n">
-        <v>671.75</v>
+        <v>667</v>
       </c>
       <c r="I46" t="n">
         <v>670.3943822133731</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.33</v>
+        <v>-3.02</v>
       </c>
       <c r="L46" t="n">
-        <v>2.86</v>
+        <v>3.17</v>
       </c>
       <c r="M46" t="n">
         <v>0.79</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>4.39</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>691</v>
+        <v>699.5</v>
       </c>
       <c r="I47" t="n">
         <v>696.2971394971428</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>11</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K47" t="n">
-        <v>-3.6</v>
+        <v>-4.87</v>
       </c>
       <c r="L47" t="n">
-        <v>5.08</v>
+        <v>5.37</v>
       </c>
       <c r="M47" t="n">
-        <v>0.27</v>
+        <v>1.45</v>
       </c>
       <c r="N47" t="n">
         <v>2.25</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>4.87</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>685.2</v>
+        <v>680.35</v>
       </c>
       <c r="I48" t="n">
         <v>680.7649852791166</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K48" t="n">
-        <v>-2.04</v>
+        <v>-2.74</v>
       </c>
       <c r="L48" t="n">
-        <v>3.07</v>
+        <v>3.42</v>
       </c>
       <c r="M48" t="n">
         <v>0.34</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>4.26</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45903.55208333334</v>
+        <v>45904.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>634.95</v>
+        <v>659.25</v>
       </c>
       <c r="I49" t="n">
         <v>651.1795920062114</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K49" t="n">
-        <v>6.67</v>
+        <v>3.1</v>
       </c>
       <c r="L49" t="n">
         <v>2.23</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>5.91</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45911.55208333334</v>
+        <v>45912.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>651.75</v>
+        <v>636.45</v>
       </c>
       <c r="I50" t="n">
         <v>638.131554934756</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K50" t="n">
-        <v>-1.14</v>
+        <v>-3.46</v>
       </c>
       <c r="L50" t="n">
-        <v>2.92</v>
+        <v>3.66</v>
       </c>
       <c r="M50" t="n">
         <v>0.49</v>
       </c>
       <c r="N50" t="n">
-        <v>1.44</v>
+        <v>2.55</v>
       </c>
       <c r="O50" t="n">
         <v>2.84</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.56</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45958.55208333334</v>
+        <v>45959.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>600.6</v>
+        <v>613.85</v>
       </c>
       <c r="I51" t="n">
         <v>606.6582775413397</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K51" t="n">
-        <v>5.63</v>
+        <v>3.55</v>
       </c>
       <c r="L51" t="n">
         <v>2.75</v>
@@ -3348,7 +3959,7 @@
         <v>0.79</v>
       </c>
       <c r="N51" t="n">
-        <v>1.95</v>
+        <v>2.06</v>
       </c>
       <c r="O51" t="n">
         <v>-2.55</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>5.23</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45965.55208333334</v>
+        <v>45967.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>594</v>
+        <v>585.5</v>
       </c>
       <c r="I52" t="n">
         <v>590.3920234988673</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.23</v>
+        <v>-4.62</v>
       </c>
       <c r="L52" t="n">
-        <v>4.11</v>
+        <v>5.27</v>
       </c>
       <c r="M52" t="n">
         <v>0.36</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>4.49</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45974.55208333334</v>
+        <v>45975.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>576</v>
+        <v>614.3</v>
       </c>
       <c r="I53" t="n">
         <v>599.8499405612944</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>1.62</v>
+        <v>-4.92</v>
       </c>
       <c r="L53" t="n">
-        <v>1.35</v>
+        <v>6.4</v>
       </c>
       <c r="M53" t="n">
-        <v>0.25</v>
+        <v>5.03</v>
       </c>
       <c r="N53" t="n">
-        <v>1.82</v>
+        <v>6.88</v>
       </c>
       <c r="O53" t="n">
         <v>-1.98</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.57</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45996.55208333334</v>
+        <v>45999.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>592.7</v>
+        <v>583.5</v>
       </c>
       <c r="I54" t="n">
         <v>584.1762046937796</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>-3.52</v>
+        <v>-5.01</v>
       </c>
       <c r="L54" t="n">
         <v>5.25</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>4.86</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46057.38541666666</v>
+        <v>46057.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>514.15</v>
+        <v>518.05</v>
       </c>
       <c r="I55" t="n">
         <v>515.7086402292689</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>58</v>
+        <v>58.16666666666666</v>
       </c>
       <c r="K55" t="n">
-        <v>11.89</v>
+        <v>11.22</v>
       </c>
       <c r="L55" t="n">
         <v>3.92</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>6.38</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46071.38541666666</v>
+        <v>46071.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>526.25</v>
+        <v>522.3</v>
       </c>
       <c r="I56" t="n">
         <v>524.6290512779826</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K56" t="n">
-        <v>1.58</v>
+        <v>0.82</v>
       </c>
       <c r="L56" t="n">
         <v>0.82</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>5.77</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46129.55208333334</v>
+        <v>46132.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>458</v>
+        <v>460.2</v>
       </c>
       <c r="I57" t="n">
         <v>459.918226713704</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>58</v>
+        <v>60.83333333333334</v>
       </c>
       <c r="K57" t="n">
-        <v>12.31</v>
+        <v>11.89</v>
       </c>
       <c r="L57" t="n">
         <v>3.47</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>9.32</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>462.25</v>
+        <v>445.65</v>
       </c>
       <c r="I58" t="n">
         <v>458.9305728155111</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K58" t="n">
-        <v>0.45</v>
+        <v>-3.16</v>
       </c>
       <c r="L58" t="n">
-        <v>2.87</v>
+        <v>3.54</v>
       </c>
       <c r="M58" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="N58" t="n">
-        <v>2.72</v>
+        <v>4.41</v>
       </c>
       <c r="O58" t="n">
         <v>-1.05</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>8.58</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46160.55208333334</v>
+        <v>46161.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>457</v>
+        <v>475.9</v>
       </c>
       <c r="I59" t="n">
         <v>471.4380004552555</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.55</v>
+        <v>-6.79</v>
       </c>
       <c r="L59" t="n">
-        <v>4.97</v>
+        <v>7.26</v>
       </c>
       <c r="M59" t="n">
         <v>0</v>
       </c>
       <c r="N59" t="n">
-        <v>2.56</v>
+        <v>4.02</v>
       </c>
       <c r="O59" t="n">
         <v>-4.41</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>9.34</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46162.55208333334</v>
+        <v>46163.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>476</v>
+        <v>437.4</v>
       </c>
       <c r="I60" t="n">
         <v>442.7003084813219</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K60" t="n">
-        <v>0.02</v>
+        <v>-8.09</v>
       </c>
       <c r="L60" t="n">
-        <v>4.5</v>
+        <v>8.76</v>
       </c>
       <c r="M60" t="n">
-        <v>0.6899999999999999</v>
+        <v>5.61</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="O60" t="n">
         <v>4.02</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>10.33</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46206.55208333334</v>
+        <v>46209.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>428.9</v>
+        <v>444.85</v>
       </c>
       <c r="I61" t="n">
         <v>437.3277740916636</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K61" t="n">
-        <v>1.94</v>
+        <v>-1.7</v>
       </c>
       <c r="L61" t="n">
-        <v>2.72</v>
+        <v>2.87</v>
       </c>
       <c r="M61" t="n">
         <v>1.41</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>3</v>
+      </c>
+      <c r="U61" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>6.91</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46216.55208333334</v>
+        <v>46217.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>432</v>
+        <v>423.35</v>
       </c>
       <c r="I62" t="n">
         <v>424.5509161071728</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.89</v>
+        <v>-4.83</v>
       </c>
       <c r="L62" t="n">
-        <v>4.12</v>
+        <v>5.09</v>
       </c>
       <c r="M62" t="n">
         <v>1.58</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>8.16</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46231.55208333334</v>
+        <v>46232.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>431.65</v>
+        <v>440</v>
       </c>
       <c r="I63" t="n">
         <v>432.2688845089489</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.96</v>
+        <v>-3.93</v>
       </c>
       <c r="L63" t="n">
-        <v>2.5</v>
+        <v>4.09</v>
       </c>
       <c r="M63" t="n">
         <v>0.93</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.07</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46265.55208333334</v>
+        <v>46266.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>489.1</v>
+        <v>486.25</v>
       </c>
       <c r="I64" t="n">
         <v>487.050042166508</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K64" t="n">
-        <v>11.16</v>
+        <v>10.51</v>
       </c>
       <c r="L64" t="n">
         <v>1.64</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.03</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46281.55208333334</v>
+        <v>46282.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>469</v>
+        <v>485.4</v>
       </c>
       <c r="I65" t="n">
         <v>484.8726349064</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K65" t="n">
-        <v>3.55</v>
+        <v>0.17</v>
       </c>
       <c r="L65" t="n">
         <v>1.29</v>
@@ -4146,7 +4925,7 @@
         <v>0.41</v>
       </c>
       <c r="N65" t="n">
-        <v>1.69</v>
+        <v>2.41</v>
       </c>
       <c r="O65" t="n">
         <v>-1.19</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>6.72</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46293.55208333334</v>
+        <v>46294.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>478.1</v>
+        <v>465.2</v>
       </c>
       <c r="I66" t="n">
         <v>472.7815843444371</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.5</v>
+        <v>-4.16</v>
       </c>
       <c r="L66" t="n">
-        <v>3.72</v>
+        <v>5.19</v>
       </c>
       <c r="M66" t="n">
         <v>0.52</v>
       </c>
       <c r="N66" t="n">
-        <v>2.49</v>
+        <v>3.03</v>
       </c>
       <c r="O66" t="n">
         <v>2.41</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>6.52</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46321.55208333334</v>
+        <v>46322.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>422.95</v>
+        <v>423.85</v>
       </c>
       <c r="I67" t="n">
         <v>423.7380801626955</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K67" t="n">
-        <v>9.08</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L67" t="n">
         <v>2.87</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4320,6 +5135,12 @@
       <c r="Q68" t="n">
         <v>2</v>
       </c>
+      <c r="R68" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6422,7 +7243,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.4</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="6">
@@ -6432,7 +7253,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.7</v>
+        <v>18.9</v>
       </c>
     </row>
     <row r="7">
@@ -6442,7 +7263,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>153.2</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8">
@@ -6452,7 +7273,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6462,7 +7283,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
     </row>
     <row r="10">
@@ -6472,7 +7293,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50.1</v>
+        <v>51.6</v>
       </c>
     </row>
     <row r="11">
@@ -6512,7 +7333,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.19</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="15">
@@ -6522,7 +7343,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.88</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="16">
@@ -6532,7 +7353,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.51</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17">
@@ -6542,7 +7363,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>48.01</v>
+        <v>42.73</v>
       </c>
     </row>
     <row r="18">
@@ -6552,7 +7373,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="19">
@@ -6562,7 +7383,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4</v>
+        <v>4.93</v>
       </c>
     </row>
     <row r="20">
@@ -6572,7 +7393,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.04</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="21">
@@ -6582,7 +7403,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>9.6</v>
+        <v>13.21</v>
       </c>
     </row>
     <row r="22">
@@ -6592,7 +7413,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
     </row>
     <row r="23">
@@ -6602,7 +7423,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -6612,7 +7433,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.2</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="25">
@@ -6622,7 +7443,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.7</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="26">
@@ -6632,7 +7453,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.07</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="27">
@@ -6642,7 +7463,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.14</v>
+        <v>12.25</v>
       </c>
     </row>
     <row r="28">
@@ -6652,7 +7473,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
